--- a/data/trans_dic/P36B13_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P36B13_R-Provincia-trans_dic.xlsx
@@ -609,7 +609,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,17%</t>
         </is>
       </c>
     </row>
@@ -632,7 +632,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11,16; 20,56</t>
+          <t>11,34; 20,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -642,22 +642,22 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,81; 18,83</t>
+          <t>10,4; 18,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,07</t>
+          <t>0,0; 1,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,88; 18,33</t>
+          <t>11,72; 17,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,48</t>
+          <t>0,0; 1,06</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,84; 16,86</t>
+          <t>10,39; 16,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,09; 7,44</t>
+          <t>1,97; 6,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,54; 10,24</t>
+          <t>5,51; 10,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,39; 4,01</t>
+          <t>1,31; 3,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,67; 12,3</t>
+          <t>8,76; 12,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,89; 4,89</t>
+          <t>1,94; 4,57</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15,17; 23,73</t>
+          <t>14,9; 23,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,08; 7,42</t>
+          <t>2,17; 6,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,15; 13,75</t>
+          <t>7,32; 13,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,33; 6,28</t>
+          <t>2,38; 6,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,15; 17,68</t>
+          <t>12,24; 17,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,8; 5,9</t>
+          <t>2,68; 5,71</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,28; 16,33</t>
+          <t>9,38; 16,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,4; 9,75</t>
+          <t>3,24; 11,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,57; 8,98</t>
+          <t>3,69; 8,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,31</t>
+          <t>0,75; 3,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,13; 11,55</t>
+          <t>7,12; 11,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,59; 5,03</t>
+          <t>2,24; 5,94</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,7; 13,68</t>
+          <t>5,86; 14,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,77</t>
+          <t>0,58; 3,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,46; 8,18</t>
+          <t>2,46; 8,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,41</t>
+          <t>0,31; 2,26</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,86; 9,78</t>
+          <t>4,94; 9,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,31</t>
+          <t>0,53; 2,25</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -1032,32 +1032,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,67; 9,78</t>
+          <t>3,72; 9,49</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,69; 7,1</t>
+          <t>1,41; 6,51</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,57; 6,13</t>
+          <t>1,41; 5,93</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,71</t>
+          <t>0,0; 2,75</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,24; 6,8</t>
+          <t>3,09; 6,78</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,87</t>
+          <t>0,9; 3,56</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>7,31%</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,49; 11,29</t>
+          <t>6,45; 11,13</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,52; 14,24</t>
+          <t>7,32; 13,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,71; 7,19</t>
+          <t>3,78; 7,11</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,61; 5,78</t>
+          <t>3,51; 6,9</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,48; 8,31</t>
+          <t>5,62; 8,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,04; 8,64</t>
+          <t>5,88; 9,16</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>11,86%</t>
         </is>
       </c>
     </row>
@@ -1192,32 +1192,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>11,8; 16,68</t>
+          <t>11,69; 16,61</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>14,53; 71,99</t>
+          <t>12,75; 19,04</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,28; 12,87</t>
+          <t>8,39; 12,8</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6,43; 10,46</t>
+          <t>6,39; 10,48</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>10,52; 13,9</t>
+          <t>10,66; 13,88</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,27; 53,13</t>
+          <t>10,22; 13,71</t>
         </is>
       </c>
     </row>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>5,63%</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>11,38; 13,65</t>
+          <t>11,42; 13,66</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6,95; 35,52</t>
+          <t>6,42; 8,7</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,03; 8,81</t>
+          <t>7,01; 8,73</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,74; 4,13</t>
+          <t>3,25; 4,56</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9,45; 10,86</t>
+          <t>9,39; 10,82</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,01; 19,71</t>
+          <t>5,02; 6,34</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1566</t>
+          <t>1088</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1566</t>
+          <t>1088</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>32609; 60070</t>
+          <t>33140; 59331</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1516,22 +1516,22 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31208; 54376</t>
+          <t>30029; 53237</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 8879</t>
+          <t>0; 5373</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>69022; 106447</t>
+          <t>68074; 103845</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 8874</t>
+          <t>0; 6748</t>
         </is>
       </c>
     </row>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>20123</t>
+          <t>20465</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12395</t>
+          <t>12671</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>32519</t>
+          <t>33136</t>
         </is>
       </c>
     </row>
@@ -1624,32 +1624,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>54486; 84729</t>
+          <t>52219; 83369</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10849; 38570</t>
+          <t>10453; 37093</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28889; 53442</t>
+          <t>28766; 52363</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7153; 20597</t>
+          <t>7143; 21344</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>88838; 125979</t>
+          <t>89730; 128858</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19546; 50427</t>
+          <t>20874; 49164</t>
         </is>
       </c>
     </row>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13403</t>
+          <t>12813</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13918</t>
+          <t>13986</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27320</t>
+          <t>26798</t>
         </is>
       </c>
     </row>
@@ -1742,32 +1742,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>47895; 74893</t>
+          <t>47036; 72742</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6502; 23158</t>
+          <t>6757; 21420</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24038; 46256</t>
+          <t>24625; 45719</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7994; 21532</t>
+          <t>8336; 22806</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>79185; 115282</t>
+          <t>79783; 115268</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18351; 38627</t>
+          <t>17757; 37804</t>
         </is>
       </c>
     </row>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>15821</t>
+          <t>22845</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5852</t>
+          <t>6976</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21673</t>
+          <t>29822</t>
         </is>
       </c>
     </row>
@@ -1860,32 +1860,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>34253; 60271</t>
+          <t>34619; 60345</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7490; 30471</t>
+          <t>12083; 41550</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13686; 34366</t>
+          <t>14132; 33100</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2410; 10986</t>
+          <t>3160; 12645</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>53630; 86875</t>
+          <t>53554; 85887</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12497; 39653</t>
+          <t>17806; 47228</t>
         </is>
       </c>
     </row>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2971</t>
+          <t>3258</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1841</t>
+          <t>1893</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4812</t>
+          <t>5151</t>
         </is>
       </c>
     </row>
@@ -1978,32 +1978,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>11982; 28748</t>
+          <t>12322; 29887</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1130; 6744</t>
+          <t>1198; 7660</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5362; 17805</t>
+          <t>5358; 18959</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>671; 5013</t>
+          <t>705; 5112</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>20811; 41851</t>
+          <t>21118; 41731</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2314; 8921</t>
+          <t>2271; 9728</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>9289</t>
+          <t>8567</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1406</t>
+          <t>1418</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10694</t>
+          <t>9986</t>
         </is>
       </c>
     </row>
@@ -2096,32 +2096,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>9654; 25734</t>
+          <t>9790; 24982</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4569; 19138</t>
+          <t>3806; 17617</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4278; 16752</t>
+          <t>3856; 16187</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 6978</t>
+          <t>0; 7256</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>17378; 36443</t>
+          <t>16551; 36355</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5295; 20373</t>
+          <t>4822; 19047</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>64822</t>
+          <t>70780</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>30849</t>
+          <t>38224</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95671</t>
+          <t>109004</t>
         </is>
       </c>
     </row>
@@ -2214,32 +2214,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>41762; 72650</t>
+          <t>41477; 71607</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>46971; 88894</t>
+          <t>52708; 94167</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>25248; 48932</t>
+          <t>25718; 48362</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>13669; 49007</t>
+          <t>27008; 53140</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>72509; 110022</t>
+          <t>74394; 112420</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>59403; 127247</t>
+          <t>87688; 136476</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>350833</t>
+          <t>125049</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -2309,7 +2309,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>58491</t>
+          <t>68121</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>409324</t>
+          <t>193170</t>
         </is>
       </c>
     </row>
@@ -2332,32 +2332,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>91745; 129705</t>
+          <t>90864; 129180</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>134955; 668561</t>
+          <t>101740; 151958</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>67931; 105582</t>
+          <t>68849; 105029</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>46156; 75092</t>
+          <t>53104; 87088</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>168074; 222141</t>
+          <t>170356; 221777</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>185604; 874696</t>
+          <t>166487; 223362</t>
         </is>
       </c>
     </row>
@@ -2417,7 +2417,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>477261</t>
+          <t>263777</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>126318</t>
+          <t>144376</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>603580</t>
+          <t>408153</t>
         </is>
       </c>
     </row>
@@ -2450,32 +2450,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>383818; 460533</t>
+          <t>385296; 460979</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>240232; 1227438</t>
+          <t>226688; 307138</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>247534; 310290</t>
+          <t>246674; 307483</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>100023; 150946</t>
+          <t>121123; 169961</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>651834; 748461</t>
+          <t>647309; 745995</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>356457; 1400988</t>
+          <t>364422; 459804</t>
         </is>
       </c>
     </row>
